--- a/patient_registration_form_templates/048_physical_therapy_triage_assessment--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/048_physical_therapy_triage_assessment--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -873,8 +873,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,12 +902,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'patient_1',_'value':_1}</t>
+          <t>patient_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Patient 1', 'value': 1}</t>
+          <t>Patient 1</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'patient_2',_'value':_2}</t>
+          <t>patient_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Patient 2', 'value': 2}</t>
+          <t>Patient 2</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'question_1',_'value':_'option_1'}</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Question 1', 'value': 'Option 1'}</t>
+          <t>Question 1</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'question_2',_'value':_'option_2'}</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Question 2', 'value': 'Option 2'}</t>
+          <t>Question 2</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'symptom_1',_'value':_1}</t>
+          <t>symptom_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Symptom 1', 'value': 1}</t>
+          <t>Symptom 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'symptom_2',_'value':_2}</t>
+          <t>symptom_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Symptom 2', 'value': 2}</t>
+          <t>Symptom 2</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'diagnosis_1',_'value':_1}</t>
+          <t>diagnosis_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Diagnosis 1', 'value': 1}</t>
+          <t>Diagnosis 1</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'diagnosis_2',_'value':_2}</t>
+          <t>diagnosis_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Diagnosis 2', 'value': 2}</t>
+          <t>Diagnosis 2</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'provider_1',_'value':_1}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Provider 1', 'value': 1}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'provider_2',_'value':_2}</t>
+          <t>provider_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Provider 2', 'value': 2}</t>
+          <t>Provider 2</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'staff_1',_'value':_1}</t>
+          <t>staff_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Staff 1', 'value': 1}</t>
+          <t>Staff 1</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'staff_2',_'value':_2}</t>
+          <t>staff_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Staff 2', 'value': 2}</t>
+          <t>Staff 2</t>
         </is>
       </c>
     </row>
